--- a/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_strategy_8_categories.xlsx
+++ b/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_strategy_8_categories.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R235ab12ef2d44e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R4a9674224ddf4c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Ra7f6e14949a944ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R759ed7184dcd445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="R11be03cf5bd44579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R7ac2a54a96404ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R31db7b19d73e4d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R0a2bb494f4974544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Ra61aa76a0db745f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R5b41988b97534a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Rf6ad5e60b46c41a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R17c2ee9e1d7241b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1366,10 +1366,10 @@
         <x:v>Two pair+</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="D7" s="62" t="str">
         <x:v>B</x:v>
@@ -1404,7 +1404,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="E8" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F8" s="62" t="str">
         <x:v>B</x:v>
@@ -1488,7 +1488,7 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="D11" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="E11" s="64" t="str">
         <x:v>X</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="E12" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F12" s="64" t="str">
         <x:v>X</x:v>
@@ -1578,10 +1578,10 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="E14" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F14" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="G14" s="64" t="str">
         <x:v>X</x:v>
@@ -1598,16 +1598,16 @@
         <x:v>Gutshot</x:v>
       </x:c>
       <x:c r="B15" s="56" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C15" s="56" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="E15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
         <x:v>B</x:v>
@@ -1900,7 +1900,7 @@
         <x:v>Underpair</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C10" s="49" t="str">
         <x:v>X</x:v>
@@ -1918,10 +1918,10 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="H10" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I10" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -1941,13 +1941,13 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="F11" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="G11" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="H11" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I11" s="62" t="str">
         <x:v>B</x:v>
@@ -1973,10 +1973,10 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="G12" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="H12" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I12" s="62" t="str">
         <x:v>B</x:v>
@@ -2005,10 +2005,10 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="H13" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I13" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="E15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
         <x:v>B</x:v>
@@ -2092,10 +2092,10 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="H16" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I16" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="I17" s="65" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2269,16 +2269,16 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="E7" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="F7" s="65" t="str">
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="G7" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="H7" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="I7" s="85" t="str">
         <x:v>R</x:v>
@@ -2449,7 +2449,7 @@
         <x:v>F/C</x:v>
       </x:c>
       <x:c r="G13" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="H13" s="66" t="str">
         <x:v>F/C</x:v>
@@ -2466,7 +2466,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="C14" s="41" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="D14" s="65" t="str">
         <x:v>C/R</x:v>
@@ -2475,16 +2475,16 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="F14" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="G14" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="H14" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="I14" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
@@ -2504,16 +2504,16 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="F15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="G15" s="84" t="str">
         <x:v>R</x:v>
       </x:c>
       <x:c r="H15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="I15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
@@ -2542,7 +2542,7 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="I16" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -2716,7 +2716,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="E7" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="F7" s="85" t="str">
         <x:v>R</x:v>
@@ -2748,7 +2748,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="F8" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="G8" s="64" t="str">
         <x:v>C</x:v>
@@ -2786,7 +2786,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="I9" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -2829,13 +2829,13 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="D11" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="E11" s="64" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="F11" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="G11" s="64" t="str">
         <x:v>C</x:v>
@@ -2852,13 +2852,13 @@
         <x:v>Third pair</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="C12" s="41" t="str">
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="D12" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="E12" s="64" t="str">
         <x:v>C</x:v>
@@ -2887,7 +2887,7 @@
         <x:v>F</x:v>
       </x:c>
       <x:c r="D13" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="E13" s="83" t="str">
         <x:v>F</x:v>
@@ -2951,16 +2951,16 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="F15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="G15" s="84" t="str">
         <x:v>R</x:v>
       </x:c>
       <x:c r="H15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="I15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
@@ -2986,7 +2986,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="H16" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="I16" s="66" t="str">
         <x:v>F/C</x:v>
@@ -3115,7 +3115,7 @@
         <x:v>Микс</x:v>
       </x:c>
       <x:c r="B9" s="87" t="str">
-        <x:v>Иначе два наиболее частых действия, строго 50/50</x:v>
+        <x:v>Иначе два наиболее частых действия, строго 50/50; первым указано более частое действие солвера</x:v>
       </x:c>
       <x:c r="C9" s="3"/>
       <x:c r="D9" s="3"/>

--- a/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_strategy_8_categories.xlsx
+++ b/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_strategy_8_categories.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R31db7b19d73e4d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R0a2bb494f4974544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Ra61aa76a0db745f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R5b41988b97534a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Rf6ad5e60b46c41a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R17c2ee9e1d7241b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra85cc71333af4333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="Rbf62890c679e4ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="R6f4853f8ba8d4fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R161390e09cca480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="R0c30c14b683c4ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R614a36a0afba438a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -498,18 +498,18 @@
     <x:xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
@@ -546,10 +546,10 @@
     <x:xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -821,7 +821,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>11 категорий рук × 8 категорий флопов. Чистое действие или строгий микс 50/50.</x:v>
+        <x:v>12 категорий рук × 8 категорий флопов. Чистое действие или строгий микс 50/50.</x:v>
       </x:c>
       <x:c r="B3" s="7"/>
       <x:c r="C3" s="7"/>
@@ -891,22 +891,22 @@
         <x:v>X 78.2%; B 21.8%</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
-        <x:v>X 90.5%; B 9.5%</x:v>
+        <x:v>X 90.3%; B 9.7%</x:v>
       </x:c>
       <x:c r="F6" s="17" t="n">
-        <x:v>0.0016643255305668827</x:v>
+        <x:v>0.001911111407268015</x:v>
       </x:c>
       <x:c r="G6" s="17" t="n">
-        <x:v>0.0016643255305668965</x:v>
+        <x:v>0.0019111114072680308</x:v>
       </x:c>
       <x:c r="H6" s="17" t="n">
-        <x:v>0.00017703704852457228</x:v>
+        <x:v>0.00022872305733493683</x:v>
       </x:c>
       <x:c r="I6" s="18" t="n">
         <x:v>80553</x:v>
       </x:c>
       <x:c r="J6" s="18" t="n">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -923,22 +923,22 @@
         <x:v>X 51.1%; B 48.9%</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
-        <x:v>X 49.9%; B 50.1%</x:v>
+        <x:v>X 49.6%; B 50.4%</x:v>
       </x:c>
       <x:c r="F7" s="17" t="n">
-        <x:v>0.0021432364878647115</x:v>
+        <x:v>0.002155386249347979</x:v>
       </x:c>
       <x:c r="G7" s="17" t="n">
-        <x:v>0.0016757841683597533</x:v>
+        <x:v>0.0016852839963340759</x:v>
       </x:c>
       <x:c r="H7" s="17" t="n">
-        <x:v>0.000051656670744196914</x:v>
+        <x:v>0.00005515519493037532</x:v>
       </x:c>
       <x:c r="I7" s="18" t="n">
         <x:v>61270</x:v>
       </x:c>
       <x:c r="J7" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -955,22 +955,22 @@
         <x:v>F 34.8%; C 52.4%; R 12.7%</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>F 36.1%; C 54.3%; R 9.6%</x:v>
+        <x:v>F 33.8%; C 56.6%; R 9.6%</x:v>
       </x:c>
       <x:c r="F8" s="17" t="n">
-        <x:v>0.02023559522213512</x:v>
+        <x:v>0.018660270262911356</x:v>
       </x:c>
       <x:c r="G8" s="17" t="n">
-        <x:v>0.004413500830119436</x:v>
+        <x:v>0.004069913308283823</x:v>
       </x:c>
       <x:c r="H8" s="17" t="n">
-        <x:v>0.0002328066611855719</x:v>
+        <x:v>0.00044134699951448725</x:v>
       </x:c>
       <x:c r="I8" s="18" t="n">
         <x:v>61270</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -987,22 +987,22 @@
         <x:v>F 40.0%; C 48.1%; R 11.9%</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>F 45.9%; C 46.3%; R 7.7%</x:v>
+        <x:v>F 44.2%; C 48.0%; R 7.7%</x:v>
       </x:c>
       <x:c r="F9" s="17" t="n">
-        <x:v>0.020812617277675402</x:v>
+        <x:v>0.016010458989526664</x:v>
       </x:c>
       <x:c r="G9" s="17" t="n">
-        <x:v>0.00794958217829128</x:v>
+        <x:v>0.00611535097923159</x:v>
       </x:c>
       <x:c r="H9" s="17" t="n">
-        <x:v>-0.00008647266760723402</x:v>
+        <x:v>-0.00004096079718920141</x:v>
       </x:c>
       <x:c r="I9" s="18" t="n">
         <x:v>80002</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1116,7 +1116,7 @@
       <x:c r="D16" s="23"/>
       <x:c r="E16" s="3"/>
       <x:c r="F16" s="24" t="str">
-        <x:v>11 категорий рук: 7 made, OESD, Gutshot, 2 overcards + BDFD и Air.</x:v>
+        <x:v>12 категорий рук: 8 made, OESD, Gutshot, 2 overcards + BDFD и Air.</x:v>
       </x:c>
       <x:c r="G16" s="24"/>
       <x:c r="H16" s="24"/>
@@ -1536,147 +1536,176 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="66" t="str">
+      <x:c r="B13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D13" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="E13" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G13" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H13" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I13" s="69" t="str">
+      <x:c r="E13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I13" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E14" s="69" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="F14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="41" t="str">
+      <x:c r="B15" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="C14" s="41" t="str">
+      <x:c r="C15" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="D14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E14" s="65" t="str">
+      <x:c r="D15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E15" s="65" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="F14" s="65" t="str">
+      <x:c r="F15" s="65" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="G14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="56" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="C15" s="56" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G15" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H15" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I15" s="69" t="str">
+      <x:c r="G15" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H15" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I15" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="C16" s="56" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="D16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E16" s="69" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="F16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G16" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H16" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I16" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G16" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H16" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I16" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G17" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H17" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I17" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I17" s="64" t="str">
+      <x:c r="B18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I18" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
     </x:row>
@@ -1983,147 +2012,176 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="66" t="str">
+      <x:c r="B13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D13" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="E13" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="69" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G13" s="66" t="str">
+      <x:c r="E13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G13" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="H13" s="66" t="str">
+      <x:c r="H13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I13" s="65" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="I13" s="66" t="str">
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C14" s="56" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="D14" s="69" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="E14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F14" s="66" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G14" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="H14" s="69" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="I14" s="69" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="F14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="I14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H15" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="I15" s="67" t="str">
+      <x:c r="B15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="I15" s="62" t="str">
         <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E16" s="69" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="F16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="I16" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H16" s="66" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H17" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="I16" s="66" t="str">
+      <x:c r="I17" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F17" s="65" t="str">
+      <x:c r="B18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F18" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="G17" s="65" t="str">
+      <x:c r="G18" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="H17" s="65" t="str">
+      <x:c r="H18" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="I17" s="65" t="str">
+      <x:c r="I18" s="65" t="str">
         <x:v>B/X</x:v>
       </x:c>
     </x:row>
@@ -2430,147 +2488,176 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="80" t="str">
+      <x:c r="B13" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="C13" s="80" t="str">
+      <x:c r="C13" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="D13" s="66" t="str">
+      <x:c r="D13" s="65" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="E13" s="65" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="E13" s="83" t="str">
+      <x:c r="F13" s="65" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="G13" s="65" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="H13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="80" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="F13" s="66" t="str">
+      <x:c r="C14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G14" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="G13" s="66" t="str">
-        <x:v>C/F</x:v>
-      </x:c>
-      <x:c r="H13" s="66" t="str">
+      <x:c r="H14" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="I13" s="69" t="str">
-        <x:v>C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="I14" s="69" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C14" s="41" t="str">
+      <x:c r="B15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="C15" s="41" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="D14" s="65" t="str">
+      <x:c r="D15" s="65" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="E14" s="65" t="str">
+      <x:c r="E15" s="65" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="F14" s="65" t="str">
+      <x:c r="F15" s="65" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="G14" s="65" t="str">
+      <x:c r="G15" s="65" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="H14" s="65" t="str">
+      <x:c r="H15" s="65" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="I14" s="65" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="56" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="C15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="D15" s="66" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="E15" s="66" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="F15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="G15" s="84" t="str">
-        <x:v>R</x:v>
-      </x:c>
-      <x:c r="H15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="I15" s="66" t="str">
+      <x:c r="I15" s="65" t="str">
         <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="C16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D16" s="69" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="E16" s="69" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="F16" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="G16" s="84" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H16" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="I16" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G16" s="66" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G17" s="69" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="H16" s="66" t="str">
+      <x:c r="H17" s="69" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="I16" s="66" t="str">
+      <x:c r="I17" s="69" t="str">
         <x:v>C/F</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="79" t="str">
+      <x:c r="B18" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="C17" s="79" t="str">
+      <x:c r="C18" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="D17" s="82" t="str">
+      <x:c r="D18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="E17" s="82" t="str">
+      <x:c r="E18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="F17" s="65" t="str">
+      <x:c r="F18" s="65" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="G17" s="65" t="str">
+      <x:c r="G18" s="65" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="H17" s="65" t="str">
+      <x:c r="H18" s="65" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="I17" s="65" t="str">
+      <x:c r="I18" s="65" t="str">
         <x:v>F/C</x:v>
       </x:c>
     </x:row>
@@ -2877,147 +2964,176 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="80" t="str">
+      <x:c r="B13" s="41" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="C13" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="C13" s="80" t="str">
+      <x:c r="D13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E13" s="65" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="F13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="80" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="D13" s="66" t="str">
+      <x:c r="C14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D14" s="69" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="E14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H14" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I14" s="69" t="str">
         <x:v>C/F</x:v>
       </x:c>
-      <x:c r="E13" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="F13" s="66" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="G13" s="66" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="H13" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="I13" s="69" t="str">
-        <x:v>C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C14" s="41" t="str">
+      <x:c r="B15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="C15" s="41" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="D14" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E14" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="F14" s="85" t="str">
+      <x:c r="D15" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E15" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F15" s="85" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="G14" s="85" t="str">
+      <x:c r="G15" s="85" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="H14" s="85" t="str">
+      <x:c r="H15" s="85" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="I14" s="85" t="str">
+      <x:c r="I15" s="85" t="str">
         <x:v>R</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="D15" s="69" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E15" s="69" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="F15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="G15" s="84" t="str">
-        <x:v>R</x:v>
-      </x:c>
-      <x:c r="H15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="I15" s="66" t="str">
-        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="C16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D16" s="66" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E16" s="66" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F16" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="G16" s="84" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H16" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="I16" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="68" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="69" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G16" s="69" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="H16" s="66" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="68" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="66" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G17" s="66" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H17" s="69" t="str">
         <x:v>C/F</x:v>
       </x:c>
-      <x:c r="I16" s="66" t="str">
+      <x:c r="I17" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="79" t="str">
+      <x:c r="B18" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="C17" s="79" t="str">
+      <x:c r="C18" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="D17" s="82" t="str">
+      <x:c r="D18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="E17" s="82" t="str">
+      <x:c r="E18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="F17" s="82" t="str">
+      <x:c r="F18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="G17" s="82" t="str">
+      <x:c r="G18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="H17" s="82" t="str">
+      <x:c r="H18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="I17" s="82" t="str">
+      <x:c r="I18" s="83" t="str">
         <x:v>F</x:v>
       </x:c>
     </x:row>
@@ -3145,54 +3261,58 @@
         <x:v>Категории рук</x:v>
       </x:c>
       <x:c r="B12" s="87" t="str">
-        <x:v>7 made-категорий; затем OESD; Gutshot; 2 overcards + BDFD; Air</x:v>
+        <x:v>8 made-категорий; затем OESD; Gutshot; 2 overcards + BDFD; Air</x:v>
       </x:c>
       <x:c r="C12" s="3"/>
       <x:c r="D12" s="3"/>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="87" t="str">
-        <x:v>Приоритет неготовых</x:v>
+        <x:v>Карманные пары</x:v>
       </x:c>
       <x:c r="B13" s="87" t="str">
-        <x:v>OESD &gt; Gutshot &gt; 2 overcards + BDFD &gt; Air; BDFD без двух оверкарт уходит в Air</x:v>
+        <x:v>Underpair: между top и middle; Weak pair: между middle и low; Low pocket pair: ниже low</x:v>
       </x:c>
       <x:c r="C13" s="3"/>
       <x:c r="D13" s="3"/>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="87" t="str">
-        <x:v>Категории флопов</x:v>
+        <x:v>Приоритет неготовых</x:v>
       </x:c>
       <x:c r="B14" s="87" t="str">
-        <x:v>Восемь групп — итоговые категории; B13 только детерминированно задаёт их состав</x:v>
+        <x:v>OESD &gt; Gutshot &gt; 2 overcards + BDFD &gt; Air; BDFD без двух оверкарт уходит в Air</x:v>
       </x:c>
       <x:c r="C14" s="3"/>
       <x:c r="D14" s="3"/>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="87" t="str">
-        <x:v>Роль исходной B13</x:v>
+        <x:v>Категории флопов</x:v>
       </x:c>
       <x:c r="B15" s="87" t="str">
-        <x:v>Только детерминированное описание состава новых групп</x:v>
+        <x:v>Восемь групп — итоговые категории; B13 только детерминированно задаёт их состав</x:v>
       </x:c>
       <x:c r="C15" s="3"/>
       <x:c r="D15" s="3"/>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="87" t="str">
-        <x:v>JT9</x:v>
+        <x:v>Роль исходной B13</x:v>
       </x:c>
       <x:c r="B16" s="87" t="str">
-        <x:v>Исходная B13 = [J-8]x con; в 8-групповой таблице = Middle connected</x:v>
+        <x:v>Только детерминированное описание состава новых групп</x:v>
       </x:c>
       <x:c r="C16" s="3"/>
       <x:c r="D16" s="3"/>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
-      <x:c r="A17" s="3"/>
-      <x:c r="B17" s="3"/>
+      <x:c r="A17" s="87" t="str">
+        <x:v>JT9</x:v>
+      </x:c>
+      <x:c r="B17" s="87" t="str">
+        <x:v>Исходная B13 = [J-8]x con; в 8-групповой таблице = Middle connected</x:v>
+      </x:c>
       <x:c r="C17" s="3"/>
       <x:c r="D17" s="3"/>
     </x:row>
@@ -3203,136 +3323,136 @@
       <x:c r="D18" s="3"/>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
-      <x:c r="A19" s="88" t="str">
+      <x:c r="A19" s="3"/>
+      <x:c r="B19" s="3"/>
+      <x:c r="C19" s="3"/>
+      <x:c r="D19" s="3"/>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" s="88" t="str">
         <x:v>Категория флопов</x:v>
       </x:c>
-      <x:c r="B19" s="88" t="str">
+      <x:c r="B20" s="88" t="str">
         <x:v>Входящие B13 / определение</x:v>
       </x:c>
-      <x:c r="C19" s="88" t="str">
+      <x:c r="C20" s="88" t="str">
         <x:v>Количество</x:v>
       </x:c>
-      <x:c r="D19" s="88" t="str">
+      <x:c r="D20" s="88" t="str">
         <x:v>Пояснение</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="27" customHeight="1">
-      <x:c r="A20" s="91" t="str">
-        <x:v>A-high high</x:v>
-      </x:c>
-      <x:c r="B20" s="91" t="str">
-        <x:v>ABB (6) + A[K/Q]x (16)</x:v>
-      </x:c>
-      <x:c r="C20" s="92" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D20" s="91" t="str">
-        <x:v>A с двумя broadway или с K/Q и младшей картой</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
       <x:c r="A21" s="91" t="str">
-        <x:v>A-high medium</x:v>
+        <x:v>A-high high</x:v>
       </x:c>
       <x:c r="B21" s="91" t="str">
-        <x:v>A[J-T][9-5] (10) + A[J-T][4-2] (6)</x:v>
+        <x:v>ABB (6) + A[K/Q]x (16)</x:v>
       </x:c>
       <x:c r="C21" s="92" t="n">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="91" t="str">
-        <x:v>A с J/T</x:v>
+        <x:v>A с двумя broadway или с K/Q и младшей картой</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
       <x:c r="A22" s="91" t="str">
-        <x:v>A-high low</x:v>
+        <x:v>A-high medium</x:v>
       </x:c>
       <x:c r="B22" s="91" t="str">
-        <x:v>A[9-7]x (18) + A[6-2]x (10)</x:v>
+        <x:v>A[J-T][9-5] (10) + A[J-T][4-2] (6)</x:v>
       </x:c>
       <x:c r="C22" s="92" t="n">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D22" s="91" t="str">
-        <x:v>A со средней картой 9 или ниже</x:v>
+        <x:v>A с J/T</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
       <x:c r="A23" s="91" t="str">
-        <x:v>Broadway</x:v>
+        <x:v>A-high low</x:v>
       </x:c>
       <x:c r="B23" s="91" t="str">
-        <x:v>BBB (4) + BBx (47)</x:v>
+        <x:v>A[9-7]x (18) + A[6-2]x (10)</x:v>
       </x:c>
       <x:c r="C23" s="92" t="n">
-        <x:v>51</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D23" s="91" t="str">
-        <x:v>Без A; минимум две broadway-карты</x:v>
+        <x:v>A со средней картой 9 или ниже</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
       <x:c r="A24" s="91" t="str">
-        <x:v>K/Q-high</x:v>
+        <x:v>Broadway</x:v>
       </x:c>
       <x:c r="B24" s="91" t="str">
-        <x:v>K/Qx dis (42) + K/Qx con (14)</x:v>
+        <x:v>BBB (4) + BBx (47)</x:v>
       </x:c>
       <x:c r="C24" s="92" t="n">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D24" s="91" t="str">
-        <x:v>Старшая K/Q, но не BBx</x:v>
+        <x:v>Без A; минимум две broadway-карты</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
       <x:c r="A25" s="91" t="str">
-        <x:v>Middle dry</x:v>
+        <x:v>K/Q-high</x:v>
       </x:c>
       <x:c r="B25" s="91" t="str">
-        <x:v>[J-8]x dis (67)</x:v>
+        <x:v>K/Qx dis (42) + K/Qx con (14)</x:v>
       </x:c>
       <x:c r="C25" s="92" t="n">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D25" s="91" t="str">
-        <x:v>Старшая J/T/9/8; две младшие не соседние</x:v>
+        <x:v>Старшая K/Q, но не BBx</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
       <x:c r="A26" s="91" t="str">
-        <x:v>Middle connected</x:v>
+        <x:v>Middle dry</x:v>
       </x:c>
       <x:c r="B26" s="91" t="str">
-        <x:v>[J-8]x con (26)</x:v>
+        <x:v>[J-8]x dis (67)</x:v>
       </x:c>
       <x:c r="C26" s="92" t="n">
-        <x:v>26</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D26" s="91" t="str">
-        <x:v>Старшая J/T/9/8; две младшие соседние; включает JT9</x:v>
+        <x:v>Старшая J/T/9/8; две младшие не соседние</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
       <x:c r="A27" s="91" t="str">
+        <x:v>Middle connected</x:v>
+      </x:c>
+      <x:c r="B27" s="91" t="str">
+        <x:v>[J-8]x con (26)</x:v>
+      </x:c>
+      <x:c r="C27" s="92" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D27" s="91" t="str">
+        <x:v>Старшая J/T/9/8; две младшие соседние; включает JT9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="27" customHeight="1">
+      <x:c r="A28" s="91" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="B27" s="91" t="str">
+      <x:c r="B28" s="91" t="str">
         <x:v>[7-4]x (20)</x:v>
       </x:c>
-      <x:c r="C27" s="92" t="n">
+      <x:c r="C28" s="92" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D27" s="91" t="str">
+      <x:c r="D28" s="91" t="str">
         <x:v>Старшая карта 7 или ниже</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="27" customHeight="1">
-      <x:c r="A28" s="3"/>
-      <x:c r="B28" s="3"/>
-      <x:c r="C28" s="3"/>
-      <x:c r="D28" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_strategy_8_categories.xlsx
+++ b/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_strategy_8_categories.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra85cc71333af4333"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="Rbf62890c679e4ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="R6f4853f8ba8d4fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R161390e09cca480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="R0c30c14b683c4ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R614a36a0afba438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R679eae9034534537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R34bc2d500dff43d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="R3eb5cf1e481e416a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R22f611f361bc4e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Ra86d0644a65145c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="Ra5b3ac4e0f9a4538"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1508,19 +1508,19 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
-      </x:c>
-      <x:c r="B12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E12" s="65" t="str">
-        <x:v>B/X</x:v>
+        <x:v>Weak pair</x:v>
+      </x:c>
+      <x:c r="B12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D12" s="65" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="E12" s="64" t="str">
+        <x:v>X</x:v>
       </x:c>
       <x:c r="F12" s="64" t="str">
         <x:v>X</x:v>
@@ -1528,8 +1528,8 @@
       <x:c r="G12" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="H12" s="64" t="str">
-        <x:v>X</x:v>
+      <x:c r="H12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I12" s="64" t="str">
         <x:v>X</x:v>
@@ -1537,19 +1537,19 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
-      </x:c>
-      <x:c r="B13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="65" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="E13" s="64" t="str">
-        <x:v>X</x:v>
+        <x:v>Third pair</x:v>
+      </x:c>
+      <x:c r="B13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E13" s="65" t="str">
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F13" s="64" t="str">
         <x:v>X</x:v>
@@ -1557,8 +1557,8 @@
       <x:c r="G13" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="H13" s="63" t="str">
-        <x:v>—</x:v>
+      <x:c r="H13" s="64" t="str">
+        <x:v>X</x:v>
       </x:c>
       <x:c r="I13" s="64" t="str">
         <x:v>X</x:v>
@@ -1984,60 +1984,60 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
-      </x:c>
-      <x:c r="B12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="F12" s="65" t="str">
+        <x:v>Weak pair</x:v>
+      </x:c>
+      <x:c r="B12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D12" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
+      <x:c r="E12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
       <x:c r="G12" s="65" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="H12" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I12" s="65" t="str">
         <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="H12" s="65" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="I12" s="62" t="str">
-        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
-      </x:c>
-      <x:c r="B13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="65" t="str">
+        <x:v>Third pair</x:v>
+      </x:c>
+      <x:c r="B13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F13" s="65" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="E13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
       <x:c r="G13" s="65" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="H13" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="I13" s="65" t="str">
         <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="H13" s="65" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="I13" s="62" t="str">
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -2460,28 +2460,28 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
-      </x:c>
-      <x:c r="B12" s="41" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="C12" s="41" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="D12" s="64" t="str">
-        <x:v>C</x:v>
+        <x:v>Weak pair</x:v>
+      </x:c>
+      <x:c r="B12" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C12" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D12" s="65" t="str">
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="E12" s="65" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="F12" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G12" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="H12" s="65" t="str">
-        <x:v>C/R</x:v>
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="F12" s="65" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="G12" s="65" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="H12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I12" s="64" t="str">
         <x:v>C</x:v>
@@ -2489,28 +2489,28 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
-      </x:c>
-      <x:c r="B13" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C13" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="D13" s="65" t="str">
-        <x:v>C/F</x:v>
+        <x:v>Third pair</x:v>
+      </x:c>
+      <x:c r="B13" s="41" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="C13" s="41" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="D13" s="64" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="E13" s="65" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="F13" s="65" t="str">
-        <x:v>C/F</x:v>
-      </x:c>
-      <x:c r="G13" s="65" t="str">
-        <x:v>C/F</x:v>
-      </x:c>
-      <x:c r="H13" s="63" t="str">
-        <x:v>—</x:v>
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="F13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H13" s="65" t="str">
+        <x:v>C/R</x:v>
       </x:c>
       <x:c r="I13" s="64" t="str">
         <x:v>C</x:v>
@@ -2936,28 +2936,28 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
+        <x:v>Weak pair</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="C12" s="41" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="D12" s="65" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="E12" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="F12" s="65" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="G12" s="65" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="H12" s="64" t="str">
-        <x:v>C</x:v>
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="C12" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D12" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E12" s="65" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="F12" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G12" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I12" s="64" t="str">
         <x:v>C</x:v>
@@ -2965,28 +2965,28 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
+        <x:v>Third pair</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="C13" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="D13" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E13" s="65" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="F13" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G13" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="H13" s="63" t="str">
-        <x:v>—</x:v>
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="C13" s="41" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="D13" s="65" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="E13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F13" s="65" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="G13" s="65" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="H13" s="64" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="I13" s="64" t="str">
         <x:v>C</x:v>
